--- a/output metrics.xlsx
+++ b/output metrics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shrey\Downloads\BTP\CMCNet-main-btp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{188FEE25-E020-4E84-896E-F333B0165424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{C28FF62E-74DD-49A2-9925-6EB08EC781AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{49DD9F9E-34EF-46C0-A95E-9C85B43366E4}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
   <si>
     <t>Configuration</t>
   </si>
@@ -80,6 +80,15 @@
   </si>
   <si>
     <t>experiment 4</t>
+  </si>
+  <si>
+    <t>experiment 5</t>
+  </si>
+  <si>
+    <t>Original BCE + Dice error (bidirectional gating)</t>
+  </si>
+  <si>
+    <t>threshold: 0.50</t>
   </si>
 </sst>
 </file>
@@ -464,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35BF9CAF-0262-4AE5-ACF0-6412061FE120}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
@@ -472,9 +481,10 @@
     <col min="3" max="3" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="8" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="B1" s="9" t="s">
         <v>0</v>
       </c>
@@ -497,7 +507,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>6</v>
       </c>
@@ -511,7 +521,7 @@
         <v>13</v>
       </c>
       <c r="E2" s="2">
-        <v>0.92989999999999995</v>
+        <v>0.93</v>
       </c>
       <c r="F2" s="4">
         <v>0.77429999999999999</v>
@@ -523,7 +533,7 @@
         <v>0.8569</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>7</v>
       </c>
@@ -537,7 +547,7 @@
         <v>13</v>
       </c>
       <c r="E3" s="4">
-        <v>0.83309999999999995</v>
+        <v>0.83299999999999996</v>
       </c>
       <c r="F3" s="4">
         <v>0.80479999999999996</v>
@@ -549,7 +559,7 @@
         <v>0.83520000000000005</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -563,7 +573,7 @@
         <v>13</v>
       </c>
       <c r="E4" s="4">
-        <v>0.89739999999999998</v>
+        <v>0.89700000000000002</v>
       </c>
       <c r="F4" s="4">
         <v>0.79600000000000004</v>
@@ -575,7 +585,7 @@
         <v>0.85550000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -601,29 +611,58 @@
         <v>0.8579</v>
       </c>
     </row>
-    <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+    <row r="6" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="5">
+        <v>20</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6">
+        <v>0.90300000000000002</v>
+      </c>
+      <c r="F6">
+        <v>0.82210000000000005</v>
+      </c>
+      <c r="G6">
+        <v>0.8609</v>
+      </c>
+      <c r="H6">
+        <v>0.86899999999999999</v>
+      </c>
+      <c r="I6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C7" s="3">
         <v>100</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E7" s="2">
         <v>0.91200000000000003</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F7" s="2">
         <v>0.8226</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G7" s="2">
         <v>0.86499999999999999</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H7" s="2">
         <v>0.87360000000000004</v>
       </c>
     </row>

--- a/output metrics.xlsx
+++ b/output metrics.xlsx
@@ -1,120 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shrey\Downloads\BTP\CMCNet-main-btp\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{C28FF62E-74DD-49A2-9925-6EB08EC781AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{49DD9F9E-34EF-46C0-A95E-9C85B43366E4}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
-  <si>
-    <t>Configuration</t>
-  </si>
-  <si>
-    <t>Precision</t>
-  </si>
-  <si>
-    <t>Recall</t>
-  </si>
-  <si>
-    <t>F1</t>
-  </si>
-  <si>
-    <t>mIoU</t>
-  </si>
-  <si>
-    <t>CMC-Net paper</t>
-  </si>
-  <si>
-    <t>experiment 1</t>
-  </si>
-  <si>
-    <t>experiment 2</t>
-  </si>
-  <si>
-    <t>paper baseline</t>
-  </si>
-  <si>
-    <t>experiment 3</t>
-  </si>
-  <si>
-    <t>Original BCE + Dice error</t>
-  </si>
-  <si>
-    <t>Focal Tversky error (α=0.30, β=0.70)</t>
-  </si>
-  <si>
-    <t>Focal Tversky error (α=0.45, β=0.55)</t>
-  </si>
-  <si>
-    <t>256 *256</t>
-  </si>
-  <si>
-    <t>512*512</t>
-  </si>
-  <si>
-    <t>Image Size</t>
-  </si>
-  <si>
-    <t>Epochs</t>
-  </si>
-  <si>
-    <t>experiment 4</t>
-  </si>
-  <si>
-    <t>experiment 5</t>
-  </si>
-  <si>
-    <t>Original BCE + Dice error (bidirectional gating)</t>
-  </si>
-  <si>
-    <t>threshold: 0.50</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -133,46 +54,105 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -472,202 +452,480 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35BF9CAF-0262-4AE5-ACF0-6412061FE120}">
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col width="14.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="32.7109375" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="7.28515625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="10.28515625" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="6.5703125" bestFit="1" customWidth="1" min="6" max="8"/>
+    <col width="14.28515625" bestFit="1" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="B1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="5">
+    <row r="1" ht="30" customFormat="1" customHeight="1" s="8">
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Configuration</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Epochs</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Image Size</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Recall</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>mIoU</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>experiment 1</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Original BCE + Dice error</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="2">
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>256 *256</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
         <v>0.93</v>
       </c>
-      <c r="F2" s="4">
-        <v>0.77429999999999999</v>
-      </c>
-      <c r="G2" s="4">
-        <v>0.84499999999999997</v>
-      </c>
-      <c r="H2" s="4">
+      <c r="F2" s="4" t="n">
+        <v>0.7743</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>0.845</v>
+      </c>
+      <c r="H2" s="4" t="n">
         <v>0.8569</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="5">
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>experiment 2</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Focal Tversky error (α=0.30, β=0.70)</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="4">
-        <v>0.83299999999999996</v>
-      </c>
-      <c r="F3" s="4">
-        <v>0.80479999999999996</v>
-      </c>
-      <c r="G3" s="4">
-        <v>0.81869999999999998</v>
-      </c>
-      <c r="H3" s="4">
-        <v>0.83520000000000005</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="5">
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>256 *256</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>0.8048</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>0.8187</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>0.8352000000000001</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>experiment 3</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Focal Tversky error (α=0.45, β=0.55)</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="4">
-        <v>0.89700000000000002</v>
-      </c>
-      <c r="F4" s="4">
-        <v>0.79600000000000004</v>
-      </c>
-      <c r="G4" s="4">
-        <v>0.84370000000000001</v>
-      </c>
-      <c r="H4" s="4">
-        <v>0.85550000000000004</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="5">
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>256 *256</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>0.8437</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>0.8555</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>experiment 4</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Focal Tversky error (α=0.45, β=0.55)</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="4">
-        <v>0.90100000000000002</v>
-      </c>
-      <c r="F5" s="4">
-        <v>0.79649999999999999</v>
-      </c>
-      <c r="G5" s="4">
-        <v>0.84550000000000003</v>
-      </c>
-      <c r="H5" s="4">
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>512*512</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0.901</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0.7965</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>0.8455</v>
+      </c>
+      <c r="H5" s="4" t="n">
         <v>0.8579</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="5">
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>experiment 5</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Original BCE + Dice error (bidirectional gating)</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6">
-        <v>0.90300000000000002</v>
-      </c>
-      <c r="F6">
-        <v>0.82210000000000005</v>
-      </c>
-      <c r="G6">
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>256 *256</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.8221000000000001</v>
+      </c>
+      <c r="G6" t="n">
         <v>0.8609</v>
       </c>
-      <c r="H6">
-        <v>0.86899999999999999</v>
-      </c>
-      <c r="I6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="3">
+      <c r="H6" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>threshold: 0.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" customFormat="1" s="6">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>paper baseline</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>CMC-Net paper</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0.91200000000000003</v>
-      </c>
-      <c r="F7" s="2">
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>512*512</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="F7" s="2" t="n">
         <v>0.8226</v>
       </c>
-      <c r="G7" s="2">
-        <v>0.86499999999999999</v>
-      </c>
-      <c r="H7" s="2">
-        <v>0.87360000000000004</v>
+      <c r="G7" s="2" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0.8736</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>experiment 6</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Full 100-Epoch Protocol (Cross-Gated)</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>100</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>512*512</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9237</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.7905</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8519</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.8631</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>threshold: 0.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>exp 6 (optimal)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Exp 6 + Optimal Threshold</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>512*512</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.8769</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.8448</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8605</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.8702</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>threshold: 0.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>exp 6 (safety)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Exp 6 + High-Recall Safety Mode</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>100</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>512*512</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.843</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.8719</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8572</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>threshold: 0.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>experiment 7</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BS-GDA Fusion (Defect Gating + Background Suppression)</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>100</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>512*512</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9257</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.7655</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.838</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.8522</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>threshold: 0.50 (Highest Precision)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>exp 7 (optimal)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Exp 7 + Optimal Threshold</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>100</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>512*512</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.8689</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.8377</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.853</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.8636</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>threshold: 0.04 (Peak F1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>exp 7 (safety)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Exp 7 + High-Recall Structural Safety</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>512*512</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8453000000000001</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.8583</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.8518</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.8623</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>threshold: 0.02 (+3.57% Recall vs Paper)</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>